--- a/timeTable_CE.xlsx
+++ b/timeTable_CE.xlsx
@@ -483,7 +483,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>FREE</t>
+          <t>ROSA,CE,GAPHT121,(L)</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -520,12 +520,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>FREE</t>
+          <t>ROSA,CE,GAMAT101,(L)</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>FREE</t>
+          <t>ROSA,CE,GAPHT121,(L)</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -562,7 +562,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>FREE</t>
+          <t>ZVL,CE,GMEST103,(L)</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -604,7 +604,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>FREE</t>
+          <t>ROSA,CE,GAMAT101,(L)</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -634,7 +634,7 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>FREE</t>
+          <t>ZADIE,CE,UCHUT128,(L)</t>
         </is>
       </c>
     </row>
@@ -676,7 +676,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>FREE</t>
+          <t>ZADIE,CE,UCHUT128,(L)</t>
         </is>
       </c>
     </row>

--- a/timeTable_CE.xlsx
+++ b/timeTable_CE.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="480" yWindow="4545" windowWidth="21705" windowHeight="8580" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="630" yWindow="1020" windowWidth="21375" windowHeight="11085" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet name="s1" sheetId="1" state="visible" r:id="rId1"/>
@@ -23,13 +23,18 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="3">
+  <fonts count="4">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <sz val="11"/>
     </font>
     <font>
       <name val="Calibri"/>
@@ -48,12 +53,27 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="3">
+  <borders count="4">
     <border>
       <left/>
       <right/>
       <top/>
       <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
       <diagonal/>
     </border>
     <border>
@@ -81,12 +101,15 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
     </xf>
   </cellXfs>
@@ -458,42 +481,42 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="2" t="inlineStr">
+      <c r="A1" s="3" t="inlineStr">
         <is>
           <t>week_day</t>
         </is>
       </c>
-      <c r="B1" s="2" t="inlineStr">
+      <c r="B1" s="3" t="inlineStr">
         <is>
           <t>slot_1</t>
         </is>
       </c>
-      <c r="C1" s="2" t="inlineStr">
+      <c r="C1" s="3" t="inlineStr">
         <is>
           <t>slot_2</t>
         </is>
       </c>
-      <c r="D1" s="2" t="inlineStr">
+      <c r="D1" s="3" t="inlineStr">
         <is>
           <t>slot_3</t>
         </is>
       </c>
-      <c r="E1" s="2" t="inlineStr">
+      <c r="E1" s="3" t="inlineStr">
         <is>
           <t>slot_4</t>
         </is>
       </c>
-      <c r="F1" s="2" t="inlineStr">
+      <c r="F1" s="3" t="inlineStr">
         <is>
           <t>slot_5</t>
         </is>
       </c>
-      <c r="G1" s="2" t="inlineStr">
+      <c r="G1" s="3" t="inlineStr">
         <is>
           <t>slot_6</t>
         </is>
       </c>
-      <c r="H1" s="2" t="inlineStr">
+      <c r="H1" s="3" t="inlineStr">
         <is>
           <t>slot_x</t>
         </is>
@@ -507,12 +530,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>NIVI,CE,GAPHT121,(L)</t>
+          <t>ROSA,CE,GAMAT101,(L)</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>EZRI,CE,GMEST103,(L)</t>
+          <t>FREE</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -522,7 +545,7 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>ROSA,ZVL,ZADIE,NIVI</t>
+          <t>ROSA</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -549,12 +572,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>EZRI,CE,GMEST103,(L)</t>
+          <t>FREE</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>GXEST104(T),ELVIZ,ZVL</t>
+          <t>FREE</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -564,12 +587,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>ZVL,ROSA,EZRI,EZER</t>
+          <t>ROSA</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>ZADIE,CE,UCEST105,(L)</t>
+          <t>FREE</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -591,27 +614,27 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>ANJANA,CE,GXEST104,(L)</t>
+          <t>FREE</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>GAMAT101(T),ROSA,CHINO,ELVIZ</t>
+          <t>FREE</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>ZADIE,CE,UCEST105,(L)</t>
+          <t>FREE</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>ZVL,CE,UCHUT128,(L)</t>
+          <t>FREE</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>ZADIE,CE,UCEST105,(L)</t>
+          <t>FREE</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -633,32 +656,32 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>ROSA,CE,GAMAT101,(L)</t>
+          <t>FREE</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>UCHUT128(T),ZVL</t>
+          <t>FREE</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>ROSA,CE,GAMAT101,(L)</t>
+          <t>UCEST105(P)</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>ZVL,CE,UCHUT128,(L)</t>
+          <t>ZADIE</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>UCEST105(P)</t>
+          <t>FREE</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>EZER,EZRI,ROSA,ZVL</t>
+          <t>GXEST104(T),ZVL</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -675,22 +698,22 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>NIVI,CE,GAPHT121,(L)</t>
+          <t>FREE</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>ROSA,CE,GAMAT101,(L)</t>
+          <t>FREE</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NIVI,CE,GAPHT121,(L)</t>
+          <t>FREE</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>ANJANA,CE,GXEST104,(L)</t>
+          <t>FREE</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -700,7 +723,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>ZADIE,EZER,EZRI,NIVI</t>
+          <t>ZADIE</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
